--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129034634</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129034634</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129034634</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129034634</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129034634</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129034620</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129034616</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129035008</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129035060</v>
       </c>
       <c r="B6" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>129034645</v>
       </c>
       <c r="B7" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129034640</v>
       </c>
       <c r="B8" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>129035029</v>
       </c>
       <c r="B9" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47102-2025 artfynd.xlsx
+++ b/artfynd/A 47102-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034597</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035029</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035006</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035007</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035008</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034586</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034637</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034640</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1560,6 +1605,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034645</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035060</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035001</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034632</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034634</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,6 +2125,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034584</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034581</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034616</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034618</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034620</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2565,6 +2660,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034621</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2667,6 +2767,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035049</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2769,6 +2874,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035050</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2871,6 +2981,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035051</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2973,6 +3088,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129035055</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3075,8 +3195,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129034624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>